--- a/www/download/COUNTRY.HRV.zdW16.xlsx
+++ b/www/download/COUNTRY.HRV.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Croácia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8.26250375098198</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8.33742146015543</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7.84497710826126</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6.69501075730157</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6.03039611910988</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>5.94244035252586</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5.83273391080575</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>5.35551463931815</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>4.91173222839952</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.26570960989759</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.48696297090356</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>5.33388294586426</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.8481042850087</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.70102181343767</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.73563568952309</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.598</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.578</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.603</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.633</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.637</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.683</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.719</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.768</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.696</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.632</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.572</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.531</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.57</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.247</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.221</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.238</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.274</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.279</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.298</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.321</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.356</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.401</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.391</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.318</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.269</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.254</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.246</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.304</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3036.893</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3001.987</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3056.057</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3092.179</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3137.303</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3149.281</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3240.171</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3310.082</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3438.268</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3410.056</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3294.414</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3167.11</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3022.4</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2923.053</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2966.935</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2414.731</t>
+          <t>2717704660.46223</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2366.07</t>
+          <t>2666937674.40891</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2405.113</t>
+          <t>2749285647.88613</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2483.917</t>
+          <t>2737204738.09074</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2498.072</t>
+          <t>2889741638.55864</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2536.244</t>
+          <t>2805889460.6926</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2584.097</t>
+          <t>2855240185.47796</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2651.114</t>
+          <t>2897009426.46585</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2747.62</t>
+          <t>3003443513.02517</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2730.066</t>
+          <t>2787792840.1075</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2610.403</t>
+          <t>2674452605.14853</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2510.444</t>
+          <t>2635767514.7016</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2443.903</t>
+          <t>2481902775.62649</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2405.928</t>
+          <t>2423836677.52324</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2489.511</t>
+          <t>2406801568.83427</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>959420396.661889</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>899672160.633213</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>990687435.155987</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1015071772.5007</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1108548495.16276</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1131780926.60717</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1182660132.61563</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1254136557.87557</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1334166442.55047</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1238601224.47945</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1129432247.94145</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1064151080.39283</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>979970077.351811</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>888859391.55146</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>833974684.972356</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4802556.82938423</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4091763.56752683</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3595303.53653279</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2887797.39424343</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2415958.40585681</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2296303.76737035</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1998674.19862146</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1644012.37189828</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1462871.81501225</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1537691.67872614</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1619999.12185492</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1538921.34237398</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1628904.00383574</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1670671.04243668</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1699314.89757593</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16965.549309899</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16124.3645003437</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16262.4965816717</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>17510.4605428699</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20179.1973073216</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21669.1125785004</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23080.750933232</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>26071.2244768136</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>29486.377370781</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>26227.0599775173</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>27791.8209833944</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>28724.9432260028</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>26445.2597072346</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>25442.8599107664</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>25845.283331421</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>24653.2224218151</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>23838.4508962918</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24755.2824484185</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26832.6582802561</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>31217.9986154087</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>32739.6379797724</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>35204.8534818649</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>40069.4057179876</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>45307.7628798201</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>38433.5270866229</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>40736.0387144436</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>42805.4436704337</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>39372.1371327873</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>38228.0422350248</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>38091.8870205954</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.51686435727401</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.62992465870534</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.42772131214252</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.44703583262955</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.25346208208349</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.24093191568717</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.18498698716163</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.11389579815042</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.0594282035362</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.20415251175565</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.31125240558504</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.35910487359866</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.49385471707891</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.70675882245062</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.98511578931502</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.26250375098198</t>
+          <t>769.6420580002</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.33742146015543</t>
+          <t>736.995208304222</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.84497710826126</t>
+          <t>800.503753418759</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.69501075730157</t>
+          <t>796.984840693367</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.03039611910988</t>
+          <t>866.96789204455</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.94244035252586</t>
+          <t>871.74068135806</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.83273391080575</t>
+          <t>895.350962317552</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.35551463931815</t>
+          <t>924.681711046731</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4.91173222839952</t>
+          <t>952.513381036692</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.26570960989759</t>
+          <t>890.260209648272</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5.48696297090356</t>
+          <t>857.176005177103</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>5.33388294586426</t>
+          <t>838.825716442139</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.8481042850087</t>
+          <t>781.593764088507</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5.70102181343767</t>
+          <t>713.381748945777</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>5.73563568952309</t>
+          <t>639.767011086836</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-160226109.838525</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-106023870.665307</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-107252467.880623</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-106022478.659344</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>24262110.2147674</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>92996170.0904002</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>171187442.99698</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>267719443.099062</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>306675480.692252</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>284155733.099445</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>303122992.81834</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>278149292.646485</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>286785195.782829</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>236890362.586641</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>201113526.055887</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-170055118.527671</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-124596939.648172</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-106395072.780142</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-60705343.1186591</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>52528452.9718921</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>107717451.213698</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>199523815.328513</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>281663616.730882</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>310131851.51559</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>236863859.130172</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>246337426.710396</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>243979873.908483</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>243686981.919051</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>187249631.187515</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>135426823.225938</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>9829008.68914688</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>18573068.9828647</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-857395.100480982</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>-45317135.5406846</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-28266342.7571247</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-14721281.123298</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-28336372.3315321</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>-13944173.6318202</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-3456370.82333789</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>47291873.9692728</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>56785566.1079438</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>34169418.7380017</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>43098213.8637779</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>49640731.3991256</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>65686702.8299495</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1937.08466363972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1938.24187166695</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1943.4000226248</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1950.25046323922</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1953.67927110624</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1953.51151505815</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1956.33020160649</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1954.68078360823</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1961.63292115258</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1962.26927721235</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1981.15010397535</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1978.87783575854</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1949.18129541159</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1930.95234273423</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1909.77860627819</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1900.69514847139</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1902.14687268924</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1906.66348451968</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1920.67948419275</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1920.87250020267</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1923.94157861259</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1925.54392892608</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1925.08210126086</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1931.75230485014</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1929.26677317738</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1942.86193786536</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1940.96424362677</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1922.82953515665</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1908.80813782138</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1889.64738889565</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7454.06505407591</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8323.84529712857</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9378.30535384355</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>12129.7699834328</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>14712.129237295</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>16026.7940222169</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>17961.3757665634</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>21138.1130341771</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>24827.5007767987</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>20005.6397488041</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>20528.3548759714</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>22790.1992543964</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>21186.1671353897</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22070.913807037</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>23268.5533571211</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>741568427.21242</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>760301426.936309</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>760780524.195426</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>812667527.632906</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>818553861.70752</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>781801024.263012</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>790210111.964228</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>787833280.334539</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>800532482.207617</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>694624583.902527</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>725538984.638025</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>775166730.238698</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>749482806.197537</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>771945492.789628</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>828478807.49963</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>8022.33785310043</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9099.51105788917</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11353.492142466</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>14852.7895844677</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>17510.1756775017</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>19092.5979919223</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>21677.0721238431</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>25656.490786923</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>30483.0761756188</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>22416.9174110918</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>21323.2918368754</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>23682.9732557004</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>21574.6859948492</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22813.0944522302</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>22932.3617206804</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3036.893</t>
+          <t>659056401.363158</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3001.987</t>
+          <t>764678742.544864</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3056.057</t>
+          <t>936431171.318659</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3092.179</t>
+          <t>1074279290.30543</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3137.303</t>
+          <t>1187042383.8412</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3149.281</t>
+          <t>1216877051.40214</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3240.171</t>
+          <t>1337663238.71123</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3310.082</t>
+          <t>1447889962.34468</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3438.268</t>
+          <t>1535950350.82426</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3410.056</t>
+          <t>1184104735.56083</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3294.414</t>
+          <t>1089003657.87375</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3167.11</t>
+          <t>1117471454.14956</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3022.4</t>
+          <t>1064373258.75262</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2923.053</t>
+          <t>1063060134.2101</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2966.935</t>
+          <t>1005265819.61834</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2414.731</t>
+          <t>-568.272799024517</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2366.07</t>
+          <t>-775.665760760598</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2405.113</t>
+          <t>-1975.18678862241</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2483.917</t>
+          <t>-2723.01960103483</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2498.072</t>
+          <t>-2798.04644020663</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2536.244</t>
+          <t>-3065.80396970543</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2584.097</t>
+          <t>-3715.69635727967</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2651.114</t>
+          <t>-4518.37775274596</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2747.62</t>
+          <t>-5655.57539882013</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2730.066</t>
+          <t>-2411.27766228772</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2610.403</t>
+          <t>-794.936960904028</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2510.444</t>
+          <t>-892.774001304011</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2443.903</t>
+          <t>-388.518859459501</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2405.928</t>
+          <t>-742.180645193217</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2489.511</t>
+          <t>336.191636440768</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2986.708</t>
+          <t>82512025.8492621</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2927.801</t>
+          <t>-4377315.60855484</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3036.426</t>
+          <t>-175650647.123233</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3028.853</t>
+          <t>-261611762.672523</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3204.879</t>
+          <t>-368488522.133685</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3121.824</t>
+          <t>-435076027.139132</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3193.371</t>
+          <t>-547453126.747002</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3231.585</t>
+          <t>-660056682.010146</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3387.849</t>
+          <t>-735417868.616647</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3168.019</t>
+          <t>-489480151.658308</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3049.486</t>
+          <t>-363464673.235722</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3019.204</t>
+          <t>-342304723.910859</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2854.184</t>
+          <t>-314890452.555078</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2801.254</t>
+          <t>-291114641.420476</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2406.802</t>
+          <t>-176787012.118709</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>8847.92482570321</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>9208.13332802637</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>10428.6242276699</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>13279.9045178944</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>16700.0836586941</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>17829.839281176</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>19442.4926539623</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>22580.9737842677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>26706.4042391082</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>24103.1664725168</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>22322.2894162977</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>23221.9878162258</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>20768.4318814021</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>20934.0222451293</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>20515.3573591194</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1870.236</t>
+          <t>0.0607223194838383</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1803.921</t>
+          <t>0.0749562752233299</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1806.089</t>
+          <t>0.0725781372783949</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1786.246</t>
+          <t>0.0745956521941804</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1867.918</t>
+          <t>0.0799916802151877</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1857.111</t>
+          <t>0.0824932158799122</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1871.932</t>
+          <t>0.0860732357548022</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1884.944</t>
+          <t>0.0867156204314843</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1954.647</t>
+          <t>0.0875820408366168</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1902.391</t>
+          <t>0.0782477871864482</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1824.623</t>
+          <t>0.0890682799957282</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1768.753</t>
+          <t>0.0936590075625427</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1667.031</t>
+          <t>0.0931824838753447</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1613.196</t>
+          <t>0.0992630526430255</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1633.011</t>
+          <t>0.103453370744134</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>11053.0420753764</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>11170.9246754236</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>13222.969897812</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17055.7280606209</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20099.0058384702</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21770.3847498731</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23824.2163175168</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28528.2800988921</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33710.4164008488</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>31156.3227547357</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28959.0378783993</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29897.7428783456</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27043.1761608207</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>27375.2798803056</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>27133.60860391</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1063.52</t>
+          <t>14058.2773338164</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>997.039</t>
+          <t>14227.5935239663</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1103.116</t>
+          <t>16837.9436053174</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1129.992</t>
+          <t>21722.6100515903</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1232.457</t>
+          <t>25598.350673904</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1259.359</t>
+          <t>27722.0047107369</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1319.459</t>
+          <t>30330.7892984034</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1388.279</t>
+          <t>36306.3519428676</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1486.963</t>
+          <t>42887.1134134228</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1394.057</t>
+          <t>39528.1836597952</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1270.214</t>
+          <t>35505.8379457055</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1199.064</t>
+          <t>36441.0535508881</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1104.751</t>
+          <t>32770.4694782475</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1004.792</t>
+          <t>32562.3595582048</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>833.975</t>
+          <t>31714.0152300433</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>127.05</t>
+          <t>67128.8973838885</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>137.31</t>
+          <t>68348.7251160496</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>118.03</t>
+          <t>77624.0784561411</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>98466.1562108934</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>102.69</t>
+          <t>119748.231412554</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>101.39</t>
+          <t>129901.630369209</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>143914.59109527</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>171975.873266776</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>200442.140863078</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>188542.672866955</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>105.51</t>
+          <t>174065.868749431</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>109.37</t>
+          <t>181737.676074269</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>121.22</t>
+          <t>162149.66181013</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>139.45</t>
+          <t>162405.748038515</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>198.51</t>
+          <t>158969.7574768</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>21229.742838981</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>21007.2715173725</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>22000.3339861121</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>23280.475246785</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>23433.9451083522</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>24125.4542300619</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>24752.266969072</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>25945.3535809917</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>26614.6608425461</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>25443.5333014708</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>23591.9546290086</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>23247.1951371186</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.843</t>
+          <t>22604.4129087252</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>21877.0072135027</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>21481.8922695116</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>16941.8953023991</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16623.7383861454</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>17610.7335393892</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>18378.4773554916</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>18511.9454223155</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18961.53244261</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>19460.537877538</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>20507.9131040109</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>20992.9220926295</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>20050.4162058117</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>19241.7969635339</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>19046.3054961218</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>18747.345764815</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>18444.8126801896</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>18440.7530522589</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4076.22235354227</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5123.16585096234</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5633.81102229871</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7345.14714160564</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>9578.86223348733</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10716.0032371997</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12387.1945278991</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>14912.9945495748</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>17555.131766449</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14753.0469420576</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>15503.747535474</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>17021.3703778389</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>15109.508247015</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>16120.8903170771</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>16445.9572573525</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2414731000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2366070000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2405113000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2483917000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2498072000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2536244000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2584097000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2651114000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2747620000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2730066000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2610403000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2510444000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2443903000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2405928000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2489511000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3036892694.32461</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3001987215.94689</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3056057432.89268</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3092178728.78127</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3137303428.40601</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3149280730.61517</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3240170535.52178</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3310082419.01299</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3438267974.83361</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3410056192.26195</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3294413844.9414</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3167110175.61067</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3022399604.83598</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2923053341.85277</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2966935365.30506</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1870236338.19224</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1803920705.62594</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1806089207.18025</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1786245517.06687</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1867918165.0958</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1857110779.42097</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1871931880.34484</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1884943929.55098</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1954646692.04246</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1902391364.12336</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1824622873.9101</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1768753357.6259</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1667030754.46954</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1613196319.4364</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1633010946.27834</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1597780</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1578210</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1602830</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1609940</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1633270</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1636890</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1682730</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1719450</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1779870</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1767540</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1695650</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1631720</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1571850</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1531350</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1570100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1246580</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1220730</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1237580</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1273640</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1278650</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1298300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1320890</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1356290</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1400680</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1391280</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1317620</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1268620</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1253810</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1245980</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1303560</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3036892694.32461</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3001987215.94689</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3056057432.89268</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3092178728.78127</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3137303428.40601</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3149280730.61517</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3240170535.52178</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3310082419.01299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3438267974.83361</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3410056192.26195</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3294413844.9414</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3167110175.61067</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3022399604.83598</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2923053341.85277</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2966935365.30506</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2414731000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2366070000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2405113000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2483917000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2498072000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2536244000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2584097000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2651114000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2747620000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2730066000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2610403000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2510444000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2443903000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2405928000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2489511000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>37083.09416</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>39465.1509445828</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>45977.3466223032</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>60003.324960004</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>72910.0751952982</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>80749.9531516706</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>90930.500567504</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>109151.911487152</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>127195.753066674</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>109795.537316528</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>101456.362365074</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>108097.178513553</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>97843.0746179348</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>98723.9680275546</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>97418.5872655664</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18134.51656</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>19350.7809845828</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22471.7163823032</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>29067.719840004</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>35177.2394252981</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>38437.9877416706</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>42717.971767504</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>51219.3689371525</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>60442.3184266741</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>54281.241996528</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>51009.6328350742</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>53462.4313135533</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>47879.9006979348</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>48683.2849875546</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>48159.9882282878</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>97169.92400277</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>95964.6251035126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>99789.258571368</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>102141.951619121</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>105536.738975571</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>107891.313005937</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>113496.561002833</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>114656.405770721</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>120349.69887856</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>120164.755944749</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>115660.083153095</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>114086.067572887</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>110110.943252265</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>107062.555855051</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>105620.478895896</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
